--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:38</t>
+    <t xml:space="preserve">2026-09-09 23:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:36</t>
+    <t xml:space="preserve">2026-09-18 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:25</t>
+    <t xml:space="preserve">2026-09-23 12:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:58</t>
+    <t xml:space="preserve">2026-10-02 15:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:01</t>
+    <t xml:space="preserve">2026-10-04 09:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:40</t>
+    <t xml:space="preserve">2026-10-05 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
